--- a/templates/ASANSOR_AVAN_HESAPLARI.xlsx
+++ b/templates/ASANSOR_AVAN_HESAPLARI.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRİŞ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÖZET" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 NOLU ASANSÖR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 NOLU ASANSÖR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 NOLU ASANSÖR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 NOLU ASANSÖR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MK.DAİRESİ AYD." sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOPRAKLAMA" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TABLOLAR" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SABİTLER" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GİRİŞ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ÖZET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1 NOLU ASANSÖR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2 NOLU ASANSÖR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3 NOLU ASANSÖR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4 NOLU ASANSÖR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MK.DAİRESİ AYD." sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TOPRAKLAMA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TABLOLAR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SABİTLER" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="PALANGA">TABLOLAR!$A$91:$A$92</definedName>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="twoCell">
     <from>
       <col>0</col>
@@ -536,14 +536,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -554,7 +554,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="twoCell">
     <from>
       <col>0</col>
@@ -574,14 +574,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -592,7 +592,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="twoCell">
     <from>
       <col>0</col>
@@ -612,14 +612,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -630,7 +630,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="twoCell">
     <from>
       <col>0</col>
@@ -650,14 +650,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -7540,11 +7540,11 @@
   </sheetData>
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -10223,11 +10223,11 @@
   </sheetData>
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -12906,11 +12906,11 @@
   </sheetData>
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -15589,11 +15589,11 @@
   </sheetData>
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -15701,7 +15701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15726,14 +15726,12 @@
       <c r="F1" s="58" t="n"/>
       <c r="G1" s="59" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="28">
         <f>IF(OR(GİRİŞ!$C$15="Evet",GİRİŞ!$C$16=0,GİRİŞ!$C$17=0),"Makine dairesiz ( MRL ) sistem  —  bu hesap uygulanmaz.","")</f>
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>

--- a/templates/ASANSOR_AVAN_HESAPLARI.xlsx
+++ b/templates/ASANSOR_AVAN_HESAPLARI.xlsx
@@ -5234,11 +5234,11 @@
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$C$27="","","=   ( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2)&amp;" ) · "&amp;ROUND(GİRİŞ!$C$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$C$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$C$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$C$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$C$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$C$27="","",IF(E11&lt;=0,"",(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23))*GİRİŞ!$C$27*GİRİŞ!$C$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$C$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23))*GİRİŞ!$C$27*GİRİŞ!$C$28/(SABİTLER!$C$10*E11)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -7541,10 +7541,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A135:G135"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -7917,11 +7917,11 @@
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$D$27="","","=   ( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2)&amp;" ) · "&amp;ROUND(GİRİŞ!$D$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$D$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$D$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$D$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$D$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$D$27="","",IF(E11&lt;=0,"",(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23))*GİRİŞ!$D$27*GİRİŞ!$D$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$D$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23))*GİRİŞ!$D$27*GİRİŞ!$D$28/(SABİTLER!$C$10*E11)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -10224,10 +10224,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A135:G135"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -10600,11 +10600,11 @@
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$E$27="","","=   ( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2)&amp;" ) · "&amp;ROUND(GİRİŞ!$E$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$E$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$E$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$E$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$E$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$E$27="","",IF(E11&lt;=0,"",(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23))*GİRİŞ!$E$27*GİRİŞ!$E$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$E$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23))*GİRİŞ!$E$27*GİRİŞ!$E$28/(SABİTLER!$C$10*E11)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -12907,10 +12907,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A135:G135"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -13283,11 +13283,11 @@
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$F$27="","","=   ( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2)&amp;" ) · "&amp;ROUND(GİRİŞ!$F$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$F$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$F$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$F$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$F$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$F$27="","",IF(E11&lt;=0,"",(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23))*GİRİŞ!$F$27*GİRİŞ!$F$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$F$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23))*GİRİŞ!$F$27*GİRİŞ!$F$28/(SABİTLER!$C$10*E11)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -15590,10 +15590,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A135:G135"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>

--- a/templates/ASANSOR_AVAN_HESAPLARI.xlsx
+++ b/templates/ASANSOR_AVAN_HESAPLARI.xlsx
@@ -3279,6 +3279,31 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>ηm</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Motorun elektrik verimi</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Şebekeden çekilen güç Pşeb = Nsç / ηm;  kolon ve makine besleme hatlarında akan odur</t>
+        </is>
+      </c>
+    </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="66" t="inlineStr">
         <is>
@@ -6848,7 +6873,7 @@
         <v/>
       </c>
       <c r="E102" s="31">
-        <f>IF(GİRİŞ!$C$27="","",GİRİŞ!$C$43*1000)</f>
+        <f>IF(GİRİŞ!$C$27="","",GİRİŞ!$C$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F102" s="30">
@@ -6996,7 +7021,7 @@
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.</t>
+          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.  Her iki hatta da motorun ŞEBEKEDEN ÇEKTİĞİ güç ( Pşeb = Nsç / ηm ) akar — Nsç mil gücüdür.</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7281,7 @@
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>Makine ( motor ) gücü</t>
+          <t>Makine besleme hattının gücü  ( = Pşeb )</t>
         </is>
       </c>
       <c r="D126" s="29" t="inlineStr">
@@ -7265,7 +7290,7 @@
         </is>
       </c>
       <c r="E126" s="31">
-        <f>IF(GİRİŞ!$C$27="","",GİRİŞ!$C$43*1000)</f>
+        <f>IF(GİRİŞ!$C$27="","",GİRİŞ!$C$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F126" s="30" t="inlineStr">
@@ -7541,10 +7566,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -9531,7 +9556,7 @@
         <v/>
       </c>
       <c r="E102" s="31">
-        <f>IF(GİRİŞ!$D$27="","",GİRİŞ!$D$43*1000)</f>
+        <f>IF(GİRİŞ!$D$27="","",GİRİŞ!$D$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F102" s="30">
@@ -9679,7 +9704,7 @@
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.</t>
+          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.  Her iki hatta da motorun ŞEBEKEDEN ÇEKTİĞİ güç ( Pşeb = Nsç / ηm ) akar — Nsç mil gücüdür.</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9964,7 @@
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>Makine ( motor ) gücü</t>
+          <t>Makine besleme hattının gücü  ( = Pşeb )</t>
         </is>
       </c>
       <c r="D126" s="29" t="inlineStr">
@@ -9948,7 +9973,7 @@
         </is>
       </c>
       <c r="E126" s="31">
-        <f>IF(GİRİŞ!$D$27="","",GİRİŞ!$D$43*1000)</f>
+        <f>IF(GİRİŞ!$D$27="","",GİRİŞ!$D$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F126" s="30" t="inlineStr">
@@ -10224,10 +10249,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -12214,7 +12239,7 @@
         <v/>
       </c>
       <c r="E102" s="31">
-        <f>IF(GİRİŞ!$E$27="","",GİRİŞ!$E$43*1000)</f>
+        <f>IF(GİRİŞ!$E$27="","",GİRİŞ!$E$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F102" s="30">
@@ -12362,7 +12387,7 @@
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.</t>
+          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.  Her iki hatta da motorun ŞEBEKEDEN ÇEKTİĞİ güç ( Pşeb = Nsç / ηm ) akar — Nsç mil gücüdür.</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12647,7 @@
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>Makine ( motor ) gücü</t>
+          <t>Makine besleme hattının gücü  ( = Pşeb )</t>
         </is>
       </c>
       <c r="D126" s="29" t="inlineStr">
@@ -12631,7 +12656,7 @@
         </is>
       </c>
       <c r="E126" s="31">
-        <f>IF(GİRİŞ!$E$27="","",GİRİŞ!$E$43*1000)</f>
+        <f>IF(GİRİŞ!$E$27="","",GİRİŞ!$E$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F126" s="30" t="inlineStr">
@@ -12907,10 +12932,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -14897,7 +14922,7 @@
         <v/>
       </c>
       <c r="E102" s="31">
-        <f>IF(GİRİŞ!$F$27="","",GİRİŞ!$F$43*1000)</f>
+        <f>IF(GİRİŞ!$F$27="","",GİRİŞ!$F$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F102" s="30">
@@ -15045,7 +15070,7 @@
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.</t>
+          <t>Kolon hattı asansörün TOPLAM kurulu gücünü ( motor + aydınlatma + priz ) taşır;  makine besleme hattı yalnız motoru besler.  Her iki hatta da motorun ŞEBEKEDEN ÇEKTİĞİ güç ( Pşeb = Nsç / ηm ) akar — Nsç mil gücüdür.</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15330,7 @@
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>Makine ( motor ) gücü</t>
+          <t>Makine besleme hattının gücü  ( = Pşeb )</t>
         </is>
       </c>
       <c r="D126" s="29" t="inlineStr">
@@ -15314,7 +15339,7 @@
         </is>
       </c>
       <c r="E126" s="31">
-        <f>IF(GİRİŞ!$F$27="","",GİRİŞ!$F$43*1000)</f>
+        <f>IF(GİRİŞ!$F$27="","",GİRİŞ!$F$43*1000/SABİTLER!$C$39)</f>
         <v/>
       </c>
       <c r="F126" s="30" t="inlineStr">
@@ -15590,10 +15615,10 @@
   <mergeCells count="65">
     <mergeCell ref="C131:G131"/>
     <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A135:G135"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>

--- a/templates/ASANSOR_AVAN_HESAPLARI.xlsx
+++ b/templates/ASANSOR_AVAN_HESAPLARI.xlsx
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Makine verimi</t>
+          <t>Toplam sistem verimi</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Dişlisiz 0,85   /   Dişli 0,50    (MMO/697 s.21)</t>
+          <t>Askı ( palanga ), kasnak ve makine kayıpları DÂHİL tek verim. Ofis kabulü: Dişlisiz 0,85 / Dişli 0,50. İmalatçı kataloğundaki toplam sistem verimini ( EN 81-20/50 şablonlarında η_ins ) doğrudan girin.</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Asansörün kendi özelliğidir. Motor GÜCÜ askı oranından bağımsızdır; askı oranı hesaba yalnız VERİM üzerinden girer ( MMO/697 §2.4 ). Boş = SABİTLER B</t>
+          <t>Asansörün kendi özelliğidir. Motor GÜCÜ askı oranından BAĞIMSIZDIR ve askı oranı verime de girmez — Δη = 0,10 palanga düşüşü kaldırılmıştır. Boş = SABİTLER B</t>
         </is>
       </c>
     </row>
@@ -2298,40 +2298,24 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Dişlisiz  η = 0,85   /   Dişli  η = 0,50   ( MMO/697 s.21 ). Seçim yalnız kaynağı belgeler; η yukarıdaki 29. satırdan gelir.</t>
+          <t>Dişlisiz  η = 0,85   /   Dişli  η = 0,50   ( ofis kabulü, TOPLAM sistem verimi ). Seçim yalnız kaynağı belgeler; η yukarıdaki 29. satırdan gelir.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Girilen η TOPLAM sistem verimi mi ?</t>
-        </is>
-      </c>
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="13" t="n"/>
       <c r="D56" s="13" t="n"/>
       <c r="E56" s="18" t="n"/>
       <c r="F56" s="18" t="n"/>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>'Evet' ise MMO/697 §2.4'teki palanga verim düşüşü ( Δη = 0,10 ) AYRICA uygulanmaz — askı kaybı zaten girilen değerin içindedir. İmalatçı kataloğundan toplam verim giriyorsanız 'Evet' seçin.</t>
-        </is>
-      </c>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="11" t="n"/>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="66" t="inlineStr">
         <is>
-          <t>Bir projede dişlili ve dişlisiz makine ya da 1:1 ve 2:1 askı birlikte kullanılabildiği için bu iki değer — makine verimi η gibi — asansöre özeldir. Boş bırakılan kolon SABİTLER B'deki ofis standardını kullanır.   Makine tipi ve askı oranı asansöre özeldir; bir projede dişlili + dişlisiz ya da 1:1 + 2:1 birlikte olabilir. MMO/697 değerleri ( dişli 1:1 = 0,50 · dişlisiz 2:1 = 0,75 ) makine verimidir ve emniyetli taraftadır; imalatçı katalogları genellikle daha yüksek TOPLAM sistem verimi verir — o değerleri kullanacaksanız 56. satırı 'Evet' yapın, yoksa palanga kaybı iki kez düşülür.</t>
+          <t>Bir projede dişlili ve dişlisiz makine ya da 1:1 ve 2:1 askı birlikte kullanılabildiği için bu iki değer — toplam sistem verimi η gibi — asansöre özeldir. Boş bırakılan kolon SABİTLER B'deki ofis standardını kullanır.   η TOPLAM SİSTEM VERİMİDİR: askı ( palanga ), kasnak ve makine kayıpları içindedir; imalatçı kataloğundaki değer ( EN 81-20/50 şablonlarında η_ins ) doğrudan girilir. MMO/697 §2.4'ün Δη = 0,10 palanga düşüşü KALDIRILMIŞTIR — makara kaybı çarpımsaldır ve sabit bir sayı çıkarmak dişli ile dişlisiz makineyi farklı oranda cezalandırıyordu.</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2346,7 @@
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="A58:H58"/>
   </mergeCells>
-  <dataValidations count="10">
+  <dataValidations count="9">
     <dataValidation sqref="C24:F24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tablo-7 dışı kapasite" error="Bu kapasite Tablo-7'de yok. Devam ederseniz anma yükü otomatik gelmez; 'Anma yükü — elle' satırını doldurun." promptTitle="Kabin kapasitesi" prompt="Listeden seçin. Tablo-7 dışı bir kapasite girerseniz anma yükünü 'Anma yükü — elle' satırına kendiniz yazmalısınız." type="list" errorStyle="warning">
       <formula1>KAPASITE</formula1>
     </dataValidation>
@@ -2390,9 +2374,6 @@
     </dataValidation>
     <dataValidation sqref="C55:F55" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Makine tipi" error="Listeden seçin: Dişlisiz / Dişli" type="list">
       <formula1>"Dişlisiz,Dişli"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C56:F56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Toplam verim" error="Listeden seçin: Hayır / Evet" type="list">
-      <formula1>"Hayır,Evet"</formula1>
     </dataValidation>
     <dataValidation sqref="C53:F53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Askı oranı" error="1 ( doğrudan askı, 1:1 )  ya da  2 ( palangalı, 2:1 )" type="list">
       <formula1>"1,2"</formula1>
@@ -2627,19 +2608,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Δη</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Palangalı sistemde verim düşüşü</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="56" t="n"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -5193,7 +5164,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Makine verimi</t>
+          <t>Toplam sistem verimi  ( askı / palanga kaybı DÂHİL )</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
@@ -5217,53 +5188,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>η′</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IF(GİRİŞ!$C$27="","",IF(GİRİŞ!$C$56="Evet","Girilen değer TOPLAM sistem verimidir — palanga düşüşü uygulanmaz","Palangalı sistemde verim ( i &gt; 1 ise η − 0,10 )"))</f>
-        <v/>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E11" s="32">
-        <f>IF(GİRİŞ!$C$27="","",IF(GİRİŞ!$C$56="Evet",GİRİŞ!$C$29,IF(IF(ISNUMBER(GİRİŞ!$C$53),GİRİŞ!$C$53,SABİTLER!$C$22)&gt;1,GİRİŞ!$C$29-SABİTLER!$C$11,GİRİŞ!$C$29)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3">
-        <f>IF(GİRİŞ!$C$56="Evet","GİRİŞ — toplam sistem verimi","SABİTLER A  /  MMO/697 §2.4")</f>
-        <v/>
-      </c>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η′ )</t>
+          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η )</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$C$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$C$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$C$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$C$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$C$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$C$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E10,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$C$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23))*GİRİŞ!$C$27*GİRİŞ!$C$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$C$27="","",IF(E10&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$C$54),GİRİŞ!$C$54,SABİTLER!$C$23))*GİRİŞ!$C$27*GİRİŞ!$C$28/(SABİTLER!$C$10*E10)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -7568,8 +7514,8 @@
     <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -7876,7 +7822,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Makine verimi</t>
+          <t>Toplam sistem verimi  ( askı / palanga kaybı DÂHİL )</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
@@ -7900,53 +7846,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>η′</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IF(GİRİŞ!$D$27="","",IF(GİRİŞ!$D$56="Evet","Girilen değer TOPLAM sistem verimidir — palanga düşüşü uygulanmaz","Palangalı sistemde verim ( i &gt; 1 ise η − 0,10 )"))</f>
-        <v/>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E11" s="32">
-        <f>IF(GİRİŞ!$D$27="","",IF(GİRİŞ!$D$56="Evet",GİRİŞ!$D$29,IF(IF(ISNUMBER(GİRİŞ!$D$53),GİRİŞ!$D$53,SABİTLER!$C$22)&gt;1,GİRİŞ!$D$29-SABİTLER!$C$11,GİRİŞ!$D$29)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3">
-        <f>IF(GİRİŞ!$D$56="Evet","GİRİŞ — toplam sistem verimi","SABİTLER A  /  MMO/697 §2.4")</f>
-        <v/>
-      </c>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η′ )</t>
+          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η )</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$D$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$D$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$D$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$D$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$D$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$D$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E10,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$D$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23))*GİRİŞ!$D$27*GİRİŞ!$D$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$D$27="","",IF(E10&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$D$54),GİRİŞ!$D$54,SABİTLER!$C$23))*GİRİŞ!$D$27*GİRİŞ!$D$28/(SABİTLER!$C$10*E10)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -10251,8 +10172,8 @@
     <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -10559,7 +10480,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Makine verimi</t>
+          <t>Toplam sistem verimi  ( askı / palanga kaybı DÂHİL )</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
@@ -10583,53 +10504,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>η′</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IF(GİRİŞ!$E$27="","",IF(GİRİŞ!$E$56="Evet","Girilen değer TOPLAM sistem verimidir — palanga düşüşü uygulanmaz","Palangalı sistemde verim ( i &gt; 1 ise η − 0,10 )"))</f>
-        <v/>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E11" s="32">
-        <f>IF(GİRİŞ!$E$27="","",IF(GİRİŞ!$E$56="Evet",GİRİŞ!$E$29,IF(IF(ISNUMBER(GİRİŞ!$E$53),GİRİŞ!$E$53,SABİTLER!$C$22)&gt;1,GİRİŞ!$E$29-SABİTLER!$C$11,GİRİŞ!$E$29)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3">
-        <f>IF(GİRİŞ!$E$56="Evet","GİRİŞ — toplam sistem verimi","SABİTLER A  /  MMO/697 §2.4")</f>
-        <v/>
-      </c>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η′ )</t>
+          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η )</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$E$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$E$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$E$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$E$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$E$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$E$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E10,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$E$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23))*GİRİŞ!$E$27*GİRİŞ!$E$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$E$27="","",IF(E10&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$E$54),GİRİŞ!$E$54,SABİTLER!$C$23))*GİRİŞ!$E$27*GİRİŞ!$E$28/(SABİTLER!$C$10*E10)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -12934,8 +12830,8 @@
     <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
@@ -13242,7 +13138,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Makine verimi</t>
+          <t>Toplam sistem verimi  ( askı / palanga kaybı DÂHİL )</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
@@ -13266,53 +13162,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>η′</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IF(GİRİŞ!$F$27="","",IF(GİRİŞ!$F$56="Evet","Girilen değer TOPLAM sistem verimidir — palanga düşüşü uygulanmaz","Palangalı sistemde verim ( i &gt; 1 ise η − 0,10 )"))</f>
-        <v/>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E11" s="32">
-        <f>IF(GİRİŞ!$F$27="","",IF(GİRİŞ!$F$56="Evet",GİRİŞ!$F$29,IF(IF(ISNUMBER(GİRİŞ!$F$53),GİRİŞ!$F$53,SABİTLER!$C$22)&gt;1,GİRİŞ!$F$29-SABİTLER!$C$11,GİRİŞ!$F$29)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3">
-        <f>IF(GİRİŞ!$F$56="Evet","GİRİŞ — toplam sistem verimi","SABİTLER A  /  MMO/697 §2.4")</f>
-        <v/>
-      </c>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η′ )</t>
+          <t>N   =   ( 1 − q ) · Q · V   /   ( 102 · η )</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="35">
-        <f>IF(GİRİŞ!$F$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$F$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$F$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E11,2)&amp;" )")</f>
+        <f>IF(GİRİŞ!$F$27="","","=   "&amp;IF(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23)&gt;=IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),"( 1 − "&amp;ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2)&amp;" )",ROUND(IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),2))&amp;" · "&amp;ROUND(GİRİŞ!$F$27,0)&amp;" · "&amp;ROUND(GİRİŞ!$F$28,2)&amp;"   /   ( 102 · "&amp;ROUND(E10,2)&amp;" )")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>IF(GİRİŞ!$F$27="","",IF(E11&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23))*GİRİŞ!$F$27*GİRİŞ!$F$28/(SABİTLER!$C$10*E11)))</f>
+        <f>IF(GİRİŞ!$F$27="","",IF(E10&lt;=0,"",MAX(1-IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23),IF(ISNUMBER(GİRİŞ!$F$54),GİRİŞ!$F$54,SABİTLER!$C$23))*GİRİŞ!$F$27*GİRİŞ!$F$28/(SABİTLER!$C$10*E10)))</f>
         <v/>
       </c>
       <c r="F14" s="37" t="inlineStr">
@@ -15617,8 +15488,8 @@
     <mergeCell ref="C92:D92"/>
     <mergeCell ref="C83:G83"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A135:G135"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E139:F139"/>
     <mergeCell ref="A116:G116"/>
     <mergeCell ref="A140:G140"/>
